--- a/Paper2_Results/Task5/task5_supporting.xlsx
+++ b/Paper2_Results/Task5/task5_supporting.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="hub_terms" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="count_vs_dwpc_top100" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="candidate_targets_by_transition" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3268,4 +3269,69 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Gene</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Largest_transition</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PDGFRA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F2→F3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tier 1 - high confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>F3→F4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Tier 1 - high confidence</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Paper2_Results/Task5/task5_supporting.xlsx
+++ b/Paper2_Results/Task5/task5_supporting.xlsx
@@ -10,6 +10,8 @@
     <sheet name="hub_terms" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="count_vs_dwpc_top100" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="candidate_targets_by_transition" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="dwpc_formula_comparison" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="candidate_convergence_per_drug" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -881,7 +883,7 @@
         <v>123</v>
       </c>
       <c r="D2" t="n">
-        <v>4.001646617146182</v>
+        <v>0.5253364728378438</v>
       </c>
       <c r="E2" t="n">
         <v>113</v>
@@ -905,7 +907,7 @@
         <v>123</v>
       </c>
       <c r="D3" t="n">
-        <v>3.987390499067373</v>
+        <v>0.5234933695541948</v>
       </c>
       <c r="E3" t="n">
         <v>113</v>
@@ -929,7 +931,7 @@
         <v>123</v>
       </c>
       <c r="D4" t="n">
-        <v>3.964297290994943</v>
+        <v>0.5205077624349922</v>
       </c>
       <c r="E4" t="n">
         <v>113</v>
@@ -946,14 +948,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ATP6V1F</t>
+          <t>ATP6V0B</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>123</v>
       </c>
       <c r="D5" t="n">
-        <v>3.915014559676345</v>
+        <v>0.5141362408595982</v>
       </c>
       <c r="E5" t="n">
         <v>113</v>
@@ -977,7 +979,7 @@
         <v>123</v>
       </c>
       <c r="D6" t="n">
-        <v>3.915014559676345</v>
+        <v>0.5141362408595982</v>
       </c>
       <c r="E6" t="n">
         <v>113</v>
@@ -994,14 +996,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ATP6V0B</t>
+          <t>ATP6V1F</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>123</v>
       </c>
       <c r="D7" t="n">
-        <v>3.915014559676345</v>
+        <v>0.5141362408595982</v>
       </c>
       <c r="E7" t="n">
         <v>113</v>
@@ -1025,7 +1027,7 @@
         <v>104</v>
       </c>
       <c r="D8" t="n">
-        <v>3.702538455814318</v>
+        <v>0.5000911527748412</v>
       </c>
       <c r="E8" t="n">
         <v>157</v>
@@ -1049,7 +1051,7 @@
         <v>123</v>
       </c>
       <c r="D9" t="n">
-        <v>3.680905480697136</v>
+        <v>0.4848714280708998</v>
       </c>
       <c r="E9" t="n">
         <v>113</v>
@@ -1066,14 +1068,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TCIRG1</t>
+          <t>ATP6V1E2</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>110</v>
       </c>
       <c r="D10" t="n">
-        <v>3.669173616292325</v>
+        <v>0.4668626970299361</v>
       </c>
       <c r="E10" t="n">
         <v>143</v>
@@ -1090,14 +1092,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ATP6V1E2</t>
+          <t>TCIRG1</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>3.669173616292325</v>
+        <v>0.4668626970299361</v>
       </c>
       <c r="E11" t="n">
         <v>143</v>
@@ -1121,7 +1123,7 @@
         <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>3.489457288525872</v>
+        <v>0.4607995735221564</v>
       </c>
       <c r="E12" t="n">
         <v>113</v>
@@ -1133,22 +1135,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHEMBL4073796</t>
+          <t>CREATINE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FGF17</t>
+          <t>GATM</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>3.479395418148437</v>
+        <v>0.3134290478896167</v>
       </c>
       <c r="E13" t="n">
-        <v>142</v>
+        <v>18858</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
@@ -1157,190 +1159,190 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PATUPILONE</t>
+          <t>FOSFOCREATINE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TUBB2B</t>
+          <t>GATM</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>276</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>3.412879513610525</v>
+        <v>0.3134290478896167</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>18858</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PATUPILONE</t>
+          <t>BUMETANIDE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TUBB6</t>
+          <t>SLC12A1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>276</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>3.412879513610525</v>
+        <v>0.2928597800124147</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>60421</v>
       </c>
       <c r="F15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EPOTHILONE D</t>
+          <t>BIOTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TUBB6</t>
+          <t>BTD</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>276</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>3.412879513610525</v>
+        <v>0.2888568655263414</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>15244</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PATUPILONE</t>
+          <t>CP-166572</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TUBB2A</t>
+          <t>DCXR</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>276</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.412879513610525</v>
+        <v>0.275945932292243</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>178645</v>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EPOTHILONE D</t>
+          <t>CP-166572</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TUBB2B</t>
+          <t>XYLB</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>276</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.412879513610525</v>
+        <v>0.275945932292243</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>178645</v>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EPOTHILONE D</t>
+          <t>CP-166572</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TUBB2A</t>
+          <t>CRYL1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>276</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.412879513610525</v>
+        <v>0.275945932292243</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>178645</v>
       </c>
       <c r="F19" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHEMBL4073796</t>
+          <t>LINACLOTIDE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FGF23</t>
+          <t>PIR</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.410055626590725</v>
+        <v>0.275945932292243</v>
       </c>
       <c r="E20" t="n">
-        <v>143</v>
+        <v>178645</v>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>BUMETANIDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PSMB7</t>
+          <t>SLC12A2</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>189</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>3.162399691832353</v>
+        <v>0.2674819709148877</v>
       </c>
       <c r="E21" t="n">
-        <v>38</v>
+        <v>60421</v>
       </c>
       <c r="F21" t="n">
         <v>20</v>
@@ -1349,190 +1351,190 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>CREATINE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PSMA4</t>
+          <t>SLC6A8</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>189</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>3.162399691832353</v>
+        <v>0.2623274314848117</v>
       </c>
       <c r="E22" t="n">
-        <v>38</v>
+        <v>26952</v>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PATUPILONE</t>
+          <t>FOSFOCREATINE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TUBB1</t>
+          <t>SLC6A8</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>245</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>3.136512669122947</v>
+        <v>0.2623274314848117</v>
       </c>
       <c r="E23" t="n">
-        <v>20</v>
+        <v>26952</v>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EPOTHILONE D</t>
+          <t>(+)-ALPHA-TOCOPHERYL SUCCINATE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TUBB1</t>
+          <t>DGKZ</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>245</v>
+        <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>3.136512669122947</v>
+        <v>0.2436754493418918</v>
       </c>
       <c r="E24" t="n">
-        <v>20</v>
+        <v>12428</v>
       </c>
       <c r="F24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PATUPILONE</t>
+          <t>(+)-ALPHA-TOCOPHERYL SUCCINATE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TUBA1A</t>
+          <t>DGKQ</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>269</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>3.118152362093821</v>
+        <v>0.2436754493418918</v>
       </c>
       <c r="E25" t="n">
-        <v>12</v>
+        <v>12428</v>
       </c>
       <c r="F25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EPOTHILONE D</t>
+          <t>RETINOL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TUBA1A</t>
+          <t>RDH10</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>269</v>
+        <v>14</v>
       </c>
       <c r="D26" t="n">
-        <v>3.118152362093821</v>
+        <v>0.2434509531916819</v>
       </c>
       <c r="E26" t="n">
-        <v>12</v>
+        <v>5867</v>
       </c>
       <c r="F26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EPOTHILONE D</t>
+          <t>RETINOL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TUBB4B</t>
+          <t>DHRS9</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>269</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>3.098001163203036</v>
+        <v>0.2434509531916819</v>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>5867</v>
       </c>
       <c r="F27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PATUPILONE</t>
+          <t>RETINOL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TUBB4B</t>
+          <t>RDH16</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>269</v>
+        <v>14</v>
       </c>
       <c r="D28" t="n">
-        <v>3.098001163203036</v>
+        <v>0.2434509531916819</v>
       </c>
       <c r="E28" t="n">
-        <v>12</v>
+        <v>5867</v>
       </c>
       <c r="F28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EPOTHILONE D</t>
+          <t>CHEMBL4073796</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TUBB3</t>
+          <t>FGF17</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>245</v>
+        <v>111</v>
       </c>
       <c r="D29" t="n">
-        <v>3.048211276033823</v>
+        <v>0.2398144901932938</v>
       </c>
       <c r="E29" t="n">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="F29" t="n">
         <v>28</v>
@@ -1541,262 +1543,262 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PATUPILONE</t>
+          <t>FOSFOCREATINE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TUBB3</t>
+          <t>SLC6A11</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>245</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>3.048211276033823</v>
+        <v>0.2375348001559365</v>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>18858</v>
       </c>
       <c r="F30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>CREATINE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PSMD13</t>
+          <t>SLC6A11</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>183</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>3.020615990880894</v>
+        <v>0.2375348001559365</v>
       </c>
       <c r="E31" t="n">
-        <v>40</v>
+        <v>18858</v>
       </c>
       <c r="F31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>PROBENECID</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PSMD1</t>
+          <t>SLC22A11</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>183</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>3.020615990880894</v>
+        <v>0.235889058896169</v>
       </c>
       <c r="E32" t="n">
-        <v>40</v>
+        <v>96297</v>
       </c>
       <c r="F32" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>CHEMBL4073796</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PSMD2</t>
+          <t>FGF23</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>183</v>
+        <v>110</v>
       </c>
       <c r="D33" t="n">
-        <v>3.020615990880894</v>
+        <v>0.2338316820494289</v>
       </c>
       <c r="E33" t="n">
-        <v>40</v>
+        <v>143</v>
       </c>
       <c r="F33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>DIACEREIN</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PSMD6</t>
+          <t>CYP2C8</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="D34" t="n">
-        <v>3.020615990880894</v>
+        <v>0.2328636845094119</v>
       </c>
       <c r="E34" t="n">
-        <v>40</v>
+        <v>2414</v>
       </c>
       <c r="F34" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>CHEMBL1224151</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PSMC4</t>
+          <t>PSEN2</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>183</v>
+        <v>24</v>
       </c>
       <c r="D35" t="n">
-        <v>3.020615990880894</v>
+        <v>0.2304874014421068</v>
       </c>
       <c r="E35" t="n">
-        <v>40</v>
+        <v>2272</v>
       </c>
       <c r="F35" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>NICOTINE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PSMD3</t>
+          <t>CHRNA4</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="D36" t="n">
-        <v>3.020615990880894</v>
+        <v>0.2303664484950887</v>
       </c>
       <c r="E36" t="n">
-        <v>40</v>
+        <v>3267</v>
       </c>
       <c r="F36" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>BUMETANIDE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PSMC2</t>
+          <t>SLC12A4</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>183</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>3.020615990880894</v>
+        <v>0.2280995301912216</v>
       </c>
       <c r="E37" t="n">
-        <v>40</v>
+        <v>60421</v>
       </c>
       <c r="F37" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>ERITADENINE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PSMD7</t>
+          <t>MAT1A</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>183</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>3.020615990880894</v>
+        <v>0.2279880426131647</v>
       </c>
       <c r="E38" t="n">
-        <v>40</v>
+        <v>60421</v>
       </c>
       <c r="F38" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>CHEMBL1224151</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PSMD12</t>
+          <t>APH1B</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>183</v>
+        <v>26</v>
       </c>
       <c r="D39" t="n">
-        <v>3.020615990880894</v>
+        <v>0.2277906070067001</v>
       </c>
       <c r="E39" t="n">
-        <v>40</v>
+        <v>2025</v>
       </c>
       <c r="F39" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>GLUTATHIONE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PSMD14</t>
+          <t>GSTM4</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="D40" t="n">
-        <v>3.000032157370824</v>
+        <v>0.2268476845508443</v>
       </c>
       <c r="E40" t="n">
-        <v>40</v>
+        <v>3595</v>
       </c>
       <c r="F40" t="n">
         <v>39</v>
@@ -1805,166 +1807,166 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>BARDOXOLONE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PSMC1</t>
+          <t>FADD</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>183</v>
+        <v>14</v>
       </c>
       <c r="D41" t="n">
-        <v>3.000032157370824</v>
+        <v>0.2266917998737499</v>
       </c>
       <c r="E41" t="n">
+        <v>5867</v>
+      </c>
+      <c r="F41" t="n">
         <v>40</v>
-      </c>
-      <c r="F41" t="n">
-        <v>39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>ORNITHINE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PSMC6</t>
+          <t>NAGS</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>183</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>3.000032157370824</v>
+        <v>0.2261334488464611</v>
       </c>
       <c r="E42" t="n">
-        <v>40</v>
+        <v>34869</v>
       </c>
       <c r="F42" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PATUPILONE</t>
+          <t>ORNITHINE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TUBA1C</t>
+          <t>ASS1</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>245</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>2.931696889320458</v>
+        <v>0.2261334488464611</v>
       </c>
       <c r="E43" t="n">
-        <v>20</v>
+        <v>34869</v>
       </c>
       <c r="F43" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EPOTHILONE D</t>
+          <t>ORNITHINE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TUBA1C</t>
+          <t>ASL</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>245</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>2.931696889320458</v>
+        <v>0.2261334488464611</v>
       </c>
       <c r="E44" t="n">
-        <v>20</v>
+        <v>34869</v>
       </c>
       <c r="F44" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PATUPILONE</t>
+          <t>ORNITHINE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TUBB4A</t>
+          <t>CPS1</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>269</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>2.912035151019925</v>
+        <v>0.2261334488464611</v>
       </c>
       <c r="E45" t="n">
-        <v>12</v>
+        <v>34869</v>
       </c>
       <c r="F45" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EPOTHILONE D</t>
+          <t>PRAMLINTIDE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TUBB4A</t>
+          <t>ADM2</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>269</v>
+        <v>8</v>
       </c>
       <c r="D46" t="n">
-        <v>2.912035151019925</v>
+        <v>0.2251320900439412</v>
       </c>
       <c r="E46" t="n">
-        <v>12</v>
+        <v>15244</v>
       </c>
       <c r="F46" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>NICOTINE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SEM1</t>
+          <t>CHRNA2</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>183</v>
+        <v>16</v>
       </c>
       <c r="D47" t="n">
-        <v>2.851259816653124</v>
+        <v>0.2241070149921875</v>
       </c>
       <c r="E47" t="n">
-        <v>40</v>
+        <v>4543</v>
       </c>
       <c r="F47" t="n">
         <v>46</v>
@@ -1973,22 +1975,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EPOTHILONE D</t>
+          <t>CHEMBL1224151</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TUBA1B</t>
+          <t>PSEN1</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>239</v>
+        <v>24</v>
       </c>
       <c r="D48" t="n">
-        <v>2.846544353857537</v>
+        <v>0.2232247519865054</v>
       </c>
       <c r="E48" t="n">
-        <v>26</v>
+        <v>2272</v>
       </c>
       <c r="F48" t="n">
         <v>47</v>
@@ -1997,46 +1999,46 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PATUPILONE</t>
+          <t>DALFAMPRIDINE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TUBA1B</t>
+          <t>KCND3</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>239</v>
+        <v>17</v>
       </c>
       <c r="D49" t="n">
-        <v>2.846544353857537</v>
+        <v>0.2224638610210118</v>
       </c>
       <c r="E49" t="n">
-        <v>26</v>
+        <v>4081</v>
       </c>
       <c r="F49" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CHEMBL291678</t>
+          <t>MENADIONE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NRAS</t>
+          <t>F10</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D50" t="n">
-        <v>2.812075596578485</v>
+        <v>0.2221688458600534</v>
       </c>
       <c r="E50" t="n">
-        <v>575</v>
+        <v>2272</v>
       </c>
       <c r="F50" t="n">
         <v>49</v>
@@ -2045,22 +2047,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CHEMBL291678</t>
+          <t>GLUTATHIONE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HRAS</t>
+          <t>GSTA5</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="D51" t="n">
-        <v>2.79495461429329</v>
+        <v>0.2200194865937565</v>
       </c>
       <c r="E51" t="n">
-        <v>575</v>
+        <v>3595</v>
       </c>
       <c r="F51" t="n">
         <v>50</v>
@@ -2069,94 +2071,94 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>GLUTATHIONE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PSMB7</t>
+          <t>ESD</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="D52" t="n">
-        <v>2.71290385038201</v>
+        <v>0.2200194865937565</v>
       </c>
       <c r="E52" t="n">
-        <v>122</v>
+        <v>3595</v>
       </c>
       <c r="F52" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>MENADIONE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PSMB2</t>
+          <t>PROZ</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="D53" t="n">
-        <v>2.71290385038201</v>
+        <v>0.2197938284679303</v>
       </c>
       <c r="E53" t="n">
-        <v>122</v>
+        <v>4543</v>
       </c>
       <c r="F53" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>LINOLENIC ACID</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PSMA4</t>
+          <t>ELOVL1</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="D54" t="n">
-        <v>2.71290385038201</v>
+        <v>0.2172127298984549</v>
       </c>
       <c r="E54" t="n">
-        <v>122</v>
+        <v>10305</v>
       </c>
       <c r="F54" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>CREATINE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PSMC4</t>
+          <t>GAMT</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>116</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>2.661801493430203</v>
+        <v>0.2171908802383094</v>
       </c>
       <c r="E55" t="n">
-        <v>125</v>
+        <v>26952</v>
       </c>
       <c r="F55" t="n">
         <v>54</v>
@@ -2165,22 +2167,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>FOSFOCREATINE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PSMD6</t>
+          <t>GAMT</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>116</v>
+        <v>6</v>
       </c>
       <c r="D56" t="n">
-        <v>2.661801493430203</v>
+        <v>0.2171908802383094</v>
       </c>
       <c r="E56" t="n">
-        <v>125</v>
+        <v>26952</v>
       </c>
       <c r="F56" t="n">
         <v>54</v>
@@ -2189,190 +2191,190 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>BENZTHIAZIDE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PSMD7</t>
+          <t>CA14</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="D57" t="n">
-        <v>2.661801493430203</v>
+        <v>0.2159617968138453</v>
       </c>
       <c r="E57" t="n">
-        <v>125</v>
+        <v>9012</v>
       </c>
       <c r="F57" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>CYCLOTHIAZIDE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PSMC2</t>
+          <t>CA12</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="D58" t="n">
-        <v>2.661801493430203</v>
+        <v>0.2159617968138453</v>
       </c>
       <c r="E58" t="n">
-        <v>125</v>
+        <v>9012</v>
       </c>
       <c r="F58" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>BENZTHIAZIDE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PSMD3</t>
+          <t>CA12</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="D59" t="n">
-        <v>2.661801493430203</v>
+        <v>0.2159617968138453</v>
       </c>
       <c r="E59" t="n">
-        <v>125</v>
+        <v>9012</v>
       </c>
       <c r="F59" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>DALFAMPRIDINE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PSMD13</t>
+          <t>KCNAB2</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="D60" t="n">
-        <v>2.661801493430203</v>
+        <v>0.2125371266953013</v>
       </c>
       <c r="E60" t="n">
-        <v>125</v>
+        <v>4543</v>
       </c>
       <c r="F60" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>DALFAMPRIDINE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PSMD12</t>
+          <t>KCNH7</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="D61" t="n">
-        <v>2.661801493430203</v>
+        <v>0.2125371266953013</v>
       </c>
       <c r="E61" t="n">
-        <v>125</v>
+        <v>4543</v>
       </c>
       <c r="F61" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>DALFAMPRIDINE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PSMD2</t>
+          <t>KCNH1</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="D62" t="n">
-        <v>2.661801493430203</v>
+        <v>0.2125371266953013</v>
       </c>
       <c r="E62" t="n">
-        <v>125</v>
+        <v>4543</v>
       </c>
       <c r="F62" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>DALFAMPRIDINE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PSMD1</t>
+          <t>KCNAB1</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="D63" t="n">
-        <v>2.661801493430203</v>
+        <v>0.2125371266953013</v>
       </c>
       <c r="E63" t="n">
-        <v>125</v>
+        <v>4543</v>
       </c>
       <c r="F63" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>METHIONINE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PSMC6</t>
+          <t>AHCY</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>116</v>
+        <v>5</v>
       </c>
       <c r="D64" t="n">
-        <v>2.643662783000598</v>
+        <v>0.2105816509392047</v>
       </c>
       <c r="E64" t="n">
-        <v>125</v>
+        <v>34869</v>
       </c>
       <c r="F64" t="n">
         <v>63</v>
@@ -2381,22 +2383,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>METHIONINE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PSMC1</t>
+          <t>MAT1A</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>116</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>2.643662783000598</v>
+        <v>0.2105816509392047</v>
       </c>
       <c r="E65" t="n">
-        <v>125</v>
+        <v>34869</v>
       </c>
       <c r="F65" t="n">
         <v>63</v>
@@ -2405,46 +2407,46 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>BENZTHIAZIDE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PSMD14</t>
+          <t>CA13</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="D66" t="n">
-        <v>2.643662783000598</v>
+        <v>0.2101146052821727</v>
       </c>
       <c r="E66" t="n">
-        <v>125</v>
+        <v>9012</v>
       </c>
       <c r="F66" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BORTEZOMIB</t>
+          <t>GLUTATHIONE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEM1</t>
+          <t>GSTP1</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="D67" t="n">
-        <v>2.512562888178153</v>
+        <v>0.2098293743049749</v>
       </c>
       <c r="E67" t="n">
-        <v>125</v>
+        <v>1721</v>
       </c>
       <c r="F67" t="n">
         <v>66</v>
@@ -2453,22 +2455,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CHEMBL291678</t>
+          <t>SCYLLITOL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SHC1</t>
+          <t>PITPNM3</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>2.445936041599611</v>
+        <v>0.2091279105182546</v>
       </c>
       <c r="E68" t="n">
-        <v>1174</v>
+        <v>178645</v>
       </c>
       <c r="F68" t="n">
         <v>67</v>
@@ -2477,310 +2479,310 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>CHEMBL1230604</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PSMA4</t>
+          <t>HGD</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>2.361719975118283</v>
+        <v>0.2091279105182546</v>
       </c>
       <c r="E69" t="n">
-        <v>391</v>
+        <v>178645</v>
       </c>
       <c r="F69" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>ACETOACETIC ACID</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PSMB7</t>
+          <t>TAT</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>2.361719975118283</v>
+        <v>0.2091279105182546</v>
       </c>
       <c r="E70" t="n">
-        <v>391</v>
+        <v>178645</v>
       </c>
       <c r="F70" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>NITISINONE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PSMB2</t>
+          <t>HGD</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>2.361719975118283</v>
+        <v>0.2091279105182546</v>
       </c>
       <c r="E71" t="n">
-        <v>391</v>
+        <v>178645</v>
       </c>
       <c r="F71" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>SCYLLITOL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PSMC4</t>
+          <t>PITPNM1</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>2.317232789488128</v>
+        <v>0.2091279105182546</v>
       </c>
       <c r="E72" t="n">
-        <v>398</v>
+        <v>178645</v>
       </c>
       <c r="F72" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>ACETOACETIC ACID</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PSMD13</t>
+          <t>HGD</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>2.317232789488128</v>
+        <v>0.2091279105182546</v>
       </c>
       <c r="E73" t="n">
-        <v>398</v>
+        <v>178645</v>
       </c>
       <c r="F73" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>NITISINONE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PSMC2</t>
+          <t>TAT</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>2.317232789488128</v>
+        <v>0.2091279105182546</v>
       </c>
       <c r="E74" t="n">
-        <v>398</v>
+        <v>178645</v>
       </c>
       <c r="F74" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>CP-166572</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PSMD1</t>
+          <t>AKR1A1</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>2.317232789488128</v>
+        <v>0.2091279105182546</v>
       </c>
       <c r="E75" t="n">
-        <v>398</v>
+        <v>178645</v>
       </c>
       <c r="F75" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>CHEMBL1230604</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PSMD12</t>
+          <t>TAT</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>2.317232789488128</v>
+        <v>0.2091279105182546</v>
       </c>
       <c r="E76" t="n">
-        <v>398</v>
+        <v>178645</v>
       </c>
       <c r="F76" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>FOSFOCREATINE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PSMD3</t>
+          <t>CKB</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="D77" t="n">
-        <v>2.317232789488128</v>
+        <v>0.2081846288049919</v>
       </c>
       <c r="E77" t="n">
-        <v>398</v>
+        <v>26952</v>
       </c>
       <c r="F77" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>CREATINE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PSMD6</t>
+          <t>CKB</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="D78" t="n">
-        <v>2.317232789488128</v>
+        <v>0.2081846288049919</v>
       </c>
       <c r="E78" t="n">
-        <v>398</v>
+        <v>26952</v>
       </c>
       <c r="F78" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>ADEMETIONINE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PSMD2</t>
+          <t>AHCY</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="D79" t="n">
-        <v>2.317232789488128</v>
+        <v>0.2064129158757778</v>
       </c>
       <c r="E79" t="n">
-        <v>398</v>
+        <v>15244</v>
       </c>
       <c r="F79" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>PROCAINE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PSMD7</t>
+          <t>KCNMA1</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="D80" t="n">
-        <v>2.317232789488128</v>
+        <v>0.2045020857537624</v>
       </c>
       <c r="E80" t="n">
-        <v>398</v>
+        <v>5284</v>
       </c>
       <c r="F80" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>THIOCTIC ACID</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PSMC6</t>
+          <t>LIPT2</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>2.30144212490617</v>
+        <v>0.204259137520027</v>
       </c>
       <c r="E81" t="n">
-        <v>398</v>
+        <v>96297</v>
       </c>
       <c r="F81" t="n">
         <v>80</v>
@@ -2789,94 +2791,94 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>PROCAINE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PSMC1</t>
+          <t>KCNN4</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="D82" t="n">
-        <v>2.30144212490617</v>
+        <v>0.2039610194781675</v>
       </c>
       <c r="E82" t="n">
-        <v>398</v>
+        <v>15244</v>
       </c>
       <c r="F82" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>CHEMBL377956</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PSMD14</t>
+          <t>TFPI</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>2.30144212490617</v>
+        <v>0.2033677641383304</v>
       </c>
       <c r="E83" t="n">
-        <v>398</v>
+        <v>96297</v>
       </c>
       <c r="F83" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CHEMBL291678</t>
+          <t>CHEMBL204997</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PIK3CA</t>
+          <t>TFPI</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>2.253857790600423</v>
+        <v>0.2033677641383304</v>
       </c>
       <c r="E84" t="n">
-        <v>828</v>
+        <v>96297</v>
       </c>
       <c r="F84" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CHEMBL304784</t>
+          <t>RETINOL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SEM1</t>
+          <t>ALDH8A1</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="D85" t="n">
-        <v>2.187313037620428</v>
+        <v>0.202459039870736</v>
       </c>
       <c r="E85" t="n">
-        <v>398</v>
+        <v>12428</v>
       </c>
       <c r="F85" t="n">
         <v>84</v>
@@ -2885,22 +2887,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PUROMYCIN</t>
+          <t>RETINOL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RPL3L</t>
+          <t>RDH11</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>143</v>
+        <v>14</v>
       </c>
       <c r="D86" t="n">
-        <v>2.122318576512383</v>
+        <v>0.2018660818179986</v>
       </c>
       <c r="E86" t="n">
-        <v>74</v>
+        <v>5867</v>
       </c>
       <c r="F86" t="n">
         <v>85</v>
@@ -2909,190 +2911,190 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PUROMYCIN</t>
+          <t>TRIAMTERENE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RPL22L1</t>
+          <t>SCNN1A</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>143</v>
+        <v>6</v>
       </c>
       <c r="D87" t="n">
-        <v>2.122318576512383</v>
+        <v>0.2018530166511587</v>
       </c>
       <c r="E87" t="n">
-        <v>74</v>
+        <v>26952</v>
       </c>
       <c r="F87" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PUROMYCIN</t>
+          <t>TILUDRONIC ACID</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>RPL36AL</t>
+          <t>TFR2</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="D88" t="n">
-        <v>2.122318576512383</v>
+        <v>0.2005659953595972</v>
       </c>
       <c r="E88" t="n">
-        <v>74</v>
+        <v>2272</v>
       </c>
       <c r="F88" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CHEMBL291678</t>
+          <t>TILUDRONIC ACID</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PIK3R1</t>
+          <t>HFE</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D89" t="n">
-        <v>2.109668779188651</v>
+        <v>0.2005659953595972</v>
       </c>
       <c r="E89" t="n">
-        <v>753</v>
+        <v>2272</v>
       </c>
       <c r="F89" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ANISOMYCIN</t>
+          <t>TILUDRONIC ACID</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>RPL22L1</t>
+          <t>STEAP4</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>144</v>
+        <v>24</v>
       </c>
       <c r="D90" t="n">
-        <v>2.071435001535825</v>
+        <v>0.2005659953595972</v>
       </c>
       <c r="E90" t="n">
-        <v>65</v>
+        <v>2272</v>
       </c>
       <c r="F90" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ANISOMYCIN</t>
+          <t>BIOTIN</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RPL3L</t>
+          <t>ACACB</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="D91" t="n">
-        <v>2.071435001535825</v>
+        <v>0.1978477064982816</v>
       </c>
       <c r="E91" t="n">
-        <v>65</v>
+        <v>10305</v>
       </c>
       <c r="F91" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ANISOMYCIN</t>
+          <t>DALFAMPRIDINE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RPL36AL</t>
+          <t>KCNA3</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>144</v>
+        <v>15</v>
       </c>
       <c r="D92" t="n">
-        <v>2.071435001535825</v>
+        <v>0.1962600187927246</v>
       </c>
       <c r="E92" t="n">
-        <v>65</v>
+        <v>5284</v>
       </c>
       <c r="F92" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ISOPROTERENOL</t>
+          <t>DALFAMPRIDINE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PIK3CA</t>
+          <t>KCNA2</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="D93" t="n">
-        <v>2.048050976806715</v>
+        <v>0.1962600187927246</v>
       </c>
       <c r="E93" t="n">
-        <v>138</v>
+        <v>5284</v>
       </c>
       <c r="F93" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CHEMBL1224151</t>
+          <t>DALFAMPRIDINE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>APH1B</t>
+          <t>KCND1</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D94" t="n">
-        <v>2.031148625067568</v>
+        <v>0.1958043017715304</v>
       </c>
       <c r="E94" t="n">
-        <v>2025</v>
+        <v>4081</v>
       </c>
       <c r="F94" t="n">
         <v>93</v>
@@ -3101,22 +3103,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CHEMBL1224151</t>
+          <t>PROCAINE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PSEN2</t>
+          <t>KCNMB2</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D95" t="n">
-        <v>2.011335950522064</v>
+        <v>0.1945867240081579</v>
       </c>
       <c r="E95" t="n">
-        <v>2272</v>
+        <v>7597</v>
       </c>
       <c r="F95" t="n">
         <v>94</v>
@@ -3125,22 +3127,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CARFILZOMIB</t>
+          <t>PROCAINE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PSMB2</t>
+          <t>KCNN2</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="D96" t="n">
-        <v>2.009031678959267</v>
+        <v>0.1931358649367676</v>
       </c>
       <c r="E96" t="n">
-        <v>104</v>
+        <v>10305</v>
       </c>
       <c r="F96" t="n">
         <v>95</v>
@@ -3149,22 +3151,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ALPHA-TOCOPHEROL</t>
+          <t>HISTIDINE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PPP2R1A</t>
+          <t>AMDHD1</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>1.988781377875454</v>
+        <v>0.1912880648353214</v>
       </c>
       <c r="E97" t="n">
-        <v>251</v>
+        <v>96297</v>
       </c>
       <c r="F97" t="n">
         <v>96</v>
@@ -3173,97 +3175,97 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CHEMBL1224151</t>
+          <t>HISTIDINE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PSEN1</t>
+          <t>CARNMT1</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>1.947958829452999</v>
+        <v>0.1912880648353214</v>
       </c>
       <c r="E98" t="n">
-        <v>2272</v>
+        <v>96297</v>
       </c>
       <c r="F98" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PUROMYCIN</t>
+          <t>HISTIDINE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>RPS28</t>
+          <t>UROC1</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>143</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
-        <v>1.863283397708966</v>
+        <v>0.1912880648353214</v>
       </c>
       <c r="E99" t="n">
-        <v>74</v>
+        <v>96297</v>
       </c>
       <c r="F99" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PUROMYCIN</t>
+          <t>BENTIROMIDE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RPS27L</t>
+          <t>SPINT2</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>143</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>1.863283397708966</v>
+        <v>0.1903982221807478</v>
       </c>
       <c r="E100" t="n">
-        <v>74</v>
+        <v>96297</v>
       </c>
       <c r="F100" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PUROMYCIN</t>
+          <t>BENTIROMIDE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RPS19</t>
+          <t>SPINT1</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>143</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
-        <v>1.863283397708966</v>
+        <v>0.1903982221807478</v>
       </c>
       <c r="E101" t="n">
-        <v>74</v>
+        <v>96297</v>
       </c>
       <c r="F101" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -3334,4 +3336,2504 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pairs</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Spearman, 6-factor (published) vs 4-factor</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="C2" t="n">
+        <v>439456</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>the term's degree enters twice in the published formula, because the term lies on two of the three edges</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>drug</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>drug_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>is_candidate</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>reach</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>reach_target</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>share_at_target_transition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CHEMBL1027</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TIAGABINE</t>
+        </is>
+      </c>
+      <c r="C2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CHEMBL894</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BUPROPION</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CHEMBL306700</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VILOXAZINE</t>
+        </is>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CHEMBL259621</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>(R)-2-Benzylsuccinic Acid</t>
+        </is>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CHEMBL3301595</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DASOTRALINE</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CHEMBL827</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DEXMETHYLPHENIDATE</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CHEMBL169901</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DEBRISOQUIN</t>
+        </is>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CHEMBL99946</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LEVOMILNACIPRAN</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CHEMBL1419</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SIBUTRAMINE</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CHEMBL383921</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CHEMBL383921</t>
+        </is>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CHEMBL1201208</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PHENMETRAZINE</t>
+        </is>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CHEMBL4297620</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SOLRIAMFETOL</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CHEMBL1232157</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CHEMBL1232157</t>
+        </is>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CHEMBL1118</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DESVENLAFAXINE</t>
+        </is>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CHEMBL1175</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DULOXETINE</t>
+        </is>
+      </c>
+      <c r="C16" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CHEMBL1194666</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DIETHYLPROPION</t>
+        </is>
+      </c>
+      <c r="C17" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CHEMBL637</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>VENLAFAXINE</t>
+        </is>
+      </c>
+      <c r="C18" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CHEMBL668</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PROTRIPTYLINE</t>
+        </is>
+      </c>
+      <c r="C19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CHEMBL418995</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AMINEPTINE</t>
+        </is>
+      </c>
+      <c r="C20" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CHEMBL3989690</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TESOFENSINE</t>
+        </is>
+      </c>
+      <c r="C21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CHEMBL592374</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AMITIFADINE</t>
+        </is>
+      </c>
+      <c r="C22" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CHEMBL511099</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BICIFADINE</t>
+        </is>
+      </c>
+      <c r="C23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CHEMBL14935</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TEZAMPANEL ANHYDROUS</t>
+        </is>
+      </c>
+      <c r="C24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CHEMBL1200689</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NITRIC OXIDE</t>
+        </is>
+      </c>
+      <c r="C25" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>19</v>
+      </c>
+      <c r="E25" t="n">
+        <v>11</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CHEMBL96</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GAMMA-AMINOBUTYRIC ACID</t>
+        </is>
+      </c>
+      <c r="C26" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CHEMBL1255794</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>APLAVIROC</t>
+        </is>
+      </c>
+      <c r="C27" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>22</v>
+      </c>
+      <c r="E27" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CHEMBL82301</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>VICRIVIROC</t>
+        </is>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>22</v>
+      </c>
+      <c r="E28" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CHEMBL1201187</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MARAVIROC</t>
+        </is>
+      </c>
+      <c r="C29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>22</v>
+      </c>
+      <c r="E29" t="n">
+        <v>12</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CHEMBL3545253</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FLORTAUCIPIR F 18</t>
+        </is>
+      </c>
+      <c r="C30" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>55</v>
+      </c>
+      <c r="E30" t="n">
+        <v>30</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CHEMBL1688243</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>INCB-9471</t>
+        </is>
+      </c>
+      <c r="C31" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>22</v>
+      </c>
+      <c r="E31" t="n">
+        <v>12</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CHEMBL86304</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MOCLOBEMIDE</t>
+        </is>
+      </c>
+      <c r="C32" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>41</v>
+      </c>
+      <c r="E32" t="n">
+        <v>22</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CHEMBL160347</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BROFAROMINE</t>
+        </is>
+      </c>
+      <c r="C33" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>41</v>
+      </c>
+      <c r="E33" t="n">
+        <v>22</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CHEMBL313833</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TRANYLCYPROMINE</t>
+        </is>
+      </c>
+      <c r="C34" t="b">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>41</v>
+      </c>
+      <c r="E34" t="n">
+        <v>22</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CHEMBL8706</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CLORGILINE</t>
+        </is>
+      </c>
+      <c r="C35" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>41</v>
+      </c>
+      <c r="E35" t="n">
+        <v>22</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CHEMBL1201168</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ISOCARBOXAZID</t>
+        </is>
+      </c>
+      <c r="C36" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>41</v>
+      </c>
+      <c r="E36" t="n">
+        <v>22</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CHEMBL37744</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ZIMELDINE</t>
+        </is>
+      </c>
+      <c r="C37" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>41</v>
+      </c>
+      <c r="E37" t="n">
+        <v>22</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CHEMBL972</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SELEGILINE</t>
+        </is>
+      </c>
+      <c r="C38" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>41</v>
+      </c>
+      <c r="E38" t="n">
+        <v>22</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CHEMBL673</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PARGYLINE</t>
+        </is>
+      </c>
+      <c r="C39" t="b">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>41</v>
+      </c>
+      <c r="E39" t="n">
+        <v>22</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CHEMBL131854</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>POSIZOLID</t>
+        </is>
+      </c>
+      <c r="C40" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>41</v>
+      </c>
+      <c r="E40" t="n">
+        <v>22</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CHEMBL269538</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HARMINE</t>
+        </is>
+      </c>
+      <c r="C41" t="b">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>41</v>
+      </c>
+      <c r="E41" t="n">
+        <v>22</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CHEMBL18116</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TOLOXATONE</t>
+        </is>
+      </c>
+      <c r="C42" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>41</v>
+      </c>
+      <c r="E42" t="n">
+        <v>22</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CHEMBL92401</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>IPRONIAZID</t>
+        </is>
+      </c>
+      <c r="C43" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>41</v>
+      </c>
+      <c r="E43" t="n">
+        <v>22</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CHEMBL1321</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PROCARBAZINE</t>
+        </is>
+      </c>
+      <c r="C44" t="b">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>41</v>
+      </c>
+      <c r="E44" t="n">
+        <v>22</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CHEMBL518924</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MAVORIXAFOR</t>
+        </is>
+      </c>
+      <c r="C45" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>30</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CHEMBL72006</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CHEMBL72006</t>
+        </is>
+      </c>
+      <c r="C46" t="b">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>36</v>
+      </c>
+      <c r="E46" t="n">
+        <v>19</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.5277777777777778</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CHEMBL122</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ROFECOXIB</t>
+        </is>
+      </c>
+      <c r="C47" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>91</v>
+      </c>
+      <c r="E47" t="n">
+        <v>48</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.5274725274725275</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CHEMBL184618</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FRAMYCETIN</t>
+        </is>
+      </c>
+      <c r="C48" t="b">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>21</v>
+      </c>
+      <c r="E48" t="n">
+        <v>11</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CHEMBL18442</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PLERIXAFOR</t>
+        </is>
+      </c>
+      <c r="C49" t="b">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>21</v>
+      </c>
+      <c r="E49" t="n">
+        <v>11</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CHEMBL54918</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>5-FLUOROURIDINE</t>
+        </is>
+      </c>
+      <c r="C50" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>54</v>
+      </c>
+      <c r="E50" t="n">
+        <v>28</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.5185185185185185</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CHEMBL273575</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NOMIFENSINE</t>
+        </is>
+      </c>
+      <c r="C51" t="b">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>47</v>
+      </c>
+      <c r="E51" t="n">
+        <v>24</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.5106382978723404</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CHEMBL932</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>DIPYRIDAMOLE</t>
+        </is>
+      </c>
+      <c r="C52" t="b">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>83</v>
+      </c>
+      <c r="E52" t="n">
+        <v>42</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.5060240963855421</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CHEMBL677</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LEVONORDEFRIN</t>
+        </is>
+      </c>
+      <c r="C53" t="b">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>18</v>
+      </c>
+      <c r="E53" t="n">
+        <v>9</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CHEMBL1231652</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CANALINE</t>
+        </is>
+      </c>
+      <c r="C54" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CHEMBL62836</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CHEMBL62836</t>
+        </is>
+      </c>
+      <c r="C55" t="b">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>22</v>
+      </c>
+      <c r="E55" t="n">
+        <v>11</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CHEMBL396380</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CHEMBL396380</t>
+        </is>
+      </c>
+      <c r="C56" t="b">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>6</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CHEMBL307782</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>3-AMINOBENZOIC ACID</t>
+        </is>
+      </c>
+      <c r="C57" t="b">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CHEMBL1089</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PHENELZINE</t>
+        </is>
+      </c>
+      <c r="C58" t="b">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>48</v>
+      </c>
+      <c r="E58" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CHEMBL862</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>GUANFACINE</t>
+        </is>
+      </c>
+      <c r="C59" t="b">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>18</v>
+      </c>
+      <c r="E59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CHEMBL297362</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>XYLAZINE</t>
+        </is>
+      </c>
+      <c r="C60" t="b">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>18</v>
+      </c>
+      <c r="E60" t="n">
+        <v>9</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CHEMBL2110954</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NERAMEXANE</t>
+        </is>
+      </c>
+      <c r="C61" t="b">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>8</v>
+      </c>
+      <c r="E61" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CHEMBL844</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BRIMONIDINE</t>
+        </is>
+      </c>
+      <c r="C62" t="b">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>18</v>
+      </c>
+      <c r="E62" t="n">
+        <v>9</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CHEMBL3182621</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AZD-8330</t>
+        </is>
+      </c>
+      <c r="C63" t="b">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>14</v>
+      </c>
+      <c r="E63" t="n">
+        <v>7</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CHEMBL506</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PRIMAQUINE</t>
+        </is>
+      </c>
+      <c r="C64" t="b">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>38</v>
+      </c>
+      <c r="E64" t="n">
+        <v>19</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CHEMBL1148</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>TORSEMIDE</t>
+        </is>
+      </c>
+      <c r="C65" t="b">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CHEMBL1235440</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>THIOPROLINE</t>
+        </is>
+      </c>
+      <c r="C66" t="b">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>38</v>
+      </c>
+      <c r="E66" t="n">
+        <v>19</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CHEMBL1100</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PARAMETHADIONE</t>
+        </is>
+      </c>
+      <c r="C67" t="b">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>30</v>
+      </c>
+      <c r="E67" t="n">
+        <v>15</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CHEMBL303992</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CHEMBL303992</t>
+        </is>
+      </c>
+      <c r="C68" t="b">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>22</v>
+      </c>
+      <c r="E68" t="n">
+        <v>11</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CHEMBL1313657</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CHEMBL1313657</t>
+        </is>
+      </c>
+      <c r="C69" t="b">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>18</v>
+      </c>
+      <c r="E69" t="n">
+        <v>9</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CHEMBL1233797</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CHEMBL1233797</t>
+        </is>
+      </c>
+      <c r="C70" t="b">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>38</v>
+      </c>
+      <c r="E70" t="n">
+        <v>19</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CHEMBL1574</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PHENTERMINE</t>
+        </is>
+      </c>
+      <c r="C71" t="b">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>53</v>
+      </c>
+      <c r="E71" t="n">
+        <v>26</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.4905660377358491</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CHEMBL106708</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CHEMBL106708</t>
+        </is>
+      </c>
+      <c r="C72" t="b">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>41</v>
+      </c>
+      <c r="E72" t="n">
+        <v>20</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.4878048780487805</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CHEMBL51483</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>GOSSYPOL</t>
+        </is>
+      </c>
+      <c r="C73" t="b">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>41</v>
+      </c>
+      <c r="E73" t="n">
+        <v>20</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.4878048780487805</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CHEMBL262628</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CHEMBL262628</t>
+        </is>
+      </c>
+      <c r="C74" t="b">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>29</v>
+      </c>
+      <c r="E74" t="n">
+        <v>14</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>CHEMBL218382</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CHEMBL218382</t>
+        </is>
+      </c>
+      <c r="C75" t="b">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>29</v>
+      </c>
+      <c r="E75" t="n">
+        <v>14</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CHEMBL334167</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CHEMBL334167</t>
+        </is>
+      </c>
+      <c r="C76" t="b">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>29</v>
+      </c>
+      <c r="E76" t="n">
+        <v>14</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CHEMBL331858</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>AL-7182</t>
+        </is>
+      </c>
+      <c r="C77" t="b">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>29</v>
+      </c>
+      <c r="E77" t="n">
+        <v>14</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>CHEMBL331282</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CHEMBL331282</t>
+        </is>
+      </c>
+      <c r="C78" t="b">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>29</v>
+      </c>
+      <c r="E78" t="n">
+        <v>14</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>CHEMBL328560</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SULTHIAME</t>
+        </is>
+      </c>
+      <c r="C79" t="b">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>29</v>
+      </c>
+      <c r="E79" t="n">
+        <v>14</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>CHEMBL15571</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1,2,4-TRIAZOLE</t>
+        </is>
+      </c>
+      <c r="C80" t="b">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>29</v>
+      </c>
+      <c r="E80" t="n">
+        <v>14</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CHEMBL302715</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CHEMBL302715</t>
+        </is>
+      </c>
+      <c r="C81" t="b">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>29</v>
+      </c>
+      <c r="E81" t="n">
+        <v>14</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CHEMBL273822</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CHEMBL273822</t>
+        </is>
+      </c>
+      <c r="C82" t="b">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>29</v>
+      </c>
+      <c r="E82" t="n">
+        <v>14</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CHEMBL108483</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CHEMBL108483</t>
+        </is>
+      </c>
+      <c r="C83" t="b">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>29</v>
+      </c>
+      <c r="E83" t="n">
+        <v>14</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CHEMBL386049</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>4-(2-Mercaptophenylcarboxamido)Benzenesulfonamide</t>
+        </is>
+      </c>
+      <c r="C84" t="b">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>29</v>
+      </c>
+      <c r="E84" t="n">
+        <v>14</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CHEMBL353861</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>AL-6619</t>
+        </is>
+      </c>
+      <c r="C85" t="b">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>29</v>
+      </c>
+      <c r="E85" t="n">
+        <v>14</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CHEMBL360356</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CHEMBL360356</t>
+        </is>
+      </c>
+      <c r="C86" t="b">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>29</v>
+      </c>
+      <c r="E86" t="n">
+        <v>14</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CHEMBL364869</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Indan-5-Sulfonic Acid Amide</t>
+        </is>
+      </c>
+      <c r="C87" t="b">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>29</v>
+      </c>
+      <c r="E87" t="n">
+        <v>14</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CHEMBL78755</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CHEMBL78755</t>
+        </is>
+      </c>
+      <c r="C88" t="b">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>29</v>
+      </c>
+      <c r="E88" t="n">
+        <v>14</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CHEMBL402262</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CHEMBL402262</t>
+        </is>
+      </c>
+      <c r="C89" t="b">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>29</v>
+      </c>
+      <c r="E89" t="n">
+        <v>14</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CHEMBL430879</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>CHEMBL430879</t>
+        </is>
+      </c>
+      <c r="C90" t="b">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>29</v>
+      </c>
+      <c r="E90" t="n">
+        <v>14</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>CHEMBL1235380</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CHEMBL1235380</t>
+        </is>
+      </c>
+      <c r="C91" t="b">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>29</v>
+      </c>
+      <c r="E91" t="n">
+        <v>14</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>CHEMBL1232673</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>4-Fluorobenzenesulfonamide</t>
+        </is>
+      </c>
+      <c r="C92" t="b">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>29</v>
+      </c>
+      <c r="E92" t="n">
+        <v>14</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CHEMBL476937</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>EMD-486019</t>
+        </is>
+      </c>
+      <c r="C93" t="b">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>29</v>
+      </c>
+      <c r="E93" t="n">
+        <v>14</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CHEMBL433921</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>AL-6629</t>
+        </is>
+      </c>
+      <c r="C94" t="b">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>29</v>
+      </c>
+      <c r="E94" t="n">
+        <v>14</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CHEMBL455271</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CHEMBL455271</t>
+        </is>
+      </c>
+      <c r="C95" t="b">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>29</v>
+      </c>
+      <c r="E95" t="n">
+        <v>14</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>CHEMBL408967</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CHEMBL408967</t>
+        </is>
+      </c>
+      <c r="C96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>29</v>
+      </c>
+      <c r="E96" t="n">
+        <v>14</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>CHEMBL417656</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CHEMBL417656</t>
+        </is>
+      </c>
+      <c r="C97" t="b">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>29</v>
+      </c>
+      <c r="E97" t="n">
+        <v>14</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>CHEMBL1231193</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CHEMBL1231193</t>
+        </is>
+      </c>
+      <c r="C98" t="b">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>29</v>
+      </c>
+      <c r="E98" t="n">
+        <v>14</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>CHEMBL121291</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CHEMBL121291</t>
+        </is>
+      </c>
+      <c r="C99" t="b">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>29</v>
+      </c>
+      <c r="E99" t="n">
+        <v>14</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CHEMBL1160965</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PHENYLALANYLAMINODI(ETHYLOXY)ETHYL BENZENESULFONAMIDEAMINOCARBONYLBENZENESULFONAMIDE</t>
+        </is>
+      </c>
+      <c r="C100" t="b">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>29</v>
+      </c>
+      <c r="E100" t="n">
+        <v>14</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>CHEMBL73962</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BENZOLAMIDE</t>
+        </is>
+      </c>
+      <c r="C101" t="b">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>29</v>
+      </c>
+      <c r="E101" t="n">
+        <v>14</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>